--- a/output/pdf_financials_xlsx/RCR.P.xlsx
+++ b/output/pdf_financials_xlsx/RCR.P.xlsx
@@ -11776,7 +11776,7 @@
         </is>
       </c>
       <c r="E123" s="5" t="n">
-        <v>0.303675</v>
+        <v>-0.303675</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/RCR.P.xlsx
+++ b/output/pdf_financials_xlsx/RCR.P.xlsx
@@ -1793,28 +1793,28 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.584688</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.443537</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.332938</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.203924</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.05806</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.007555</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.002061</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.001667</v>
       </c>
     </row>
     <row r="35">
@@ -1855,28 +1855,28 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.584688</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.443537</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.332938</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.203924</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.05806</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.007555</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.002061</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.001667</v>
       </c>
     </row>
     <row r="37">
@@ -2227,10 +2227,10 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.593193</v>
+        <v>0.008505</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.443537</v>
+        <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
         <v>0</v>
@@ -5222,7 +5222,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -5866,7 +5866,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E15" s="5" t="n">
